--- a/Data/EquipRandomPool.xlsx
+++ b/Data/EquipRandomPool.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D22E54AB-D3FE-457F-A78E-5A85D5AAB474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720F983E-8428-4184-B5D1-B0412433BD09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12030" yWindow="2550" windowWidth="22515" windowHeight="16245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipRandomPool" sheetId="3" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">EquipRandomPool!$A$1:$F$39</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -58,21 +61,12 @@
     <t>CritChance</t>
   </si>
   <si>
-    <t>CritDmgIncrease</t>
-  </si>
-  <si>
     <t>Accuracy</t>
   </si>
   <si>
     <t>Evasion</t>
   </si>
   <si>
-    <t>AttackSpeed</t>
-  </si>
-  <si>
-    <t>MoveSpeed</t>
-  </si>
-  <si>
     <t>Sword</t>
   </si>
   <si>
@@ -98,6 +92,15 @@
   </si>
   <si>
     <t>Defence_Inc</t>
+  </si>
+  <si>
+    <t>MoveSpeed_Inc</t>
+  </si>
+  <si>
+    <t>AttackSpeed_Inc</t>
+  </si>
+  <si>
+    <t>CritDmg_Inc</t>
   </si>
 </sst>
 </file>
@@ -502,82 +505,82 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C2">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C3">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D3">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="E3">
-        <v>0.06</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="D4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D5">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>0.03</v>
+        <v>4</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -588,27 +591,27 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D6">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>0.15</v>
+        <v>4</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -617,75 +620,75 @@
         <v>4</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8">
         <v>120</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="E8">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C9">
         <v>100</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C10">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>0.03</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11">
         <v>30</v>
@@ -697,187 +700,187 @@
         <v>0.03</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C12">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>0.03</v>
       </c>
       <c r="F12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C13">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="E13">
-        <v>4</v>
+        <v>0.06</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C14">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="D14">
-        <v>0.5</v>
+        <v>0.03</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0.08</v>
       </c>
       <c r="F14" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C15">
-        <v>140</v>
+        <v>30</v>
       </c>
       <c r="D15">
-        <v>40</v>
+        <v>0.01</v>
       </c>
       <c r="E15">
-        <v>120</v>
+        <v>0.03</v>
       </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C16">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="D16">
-        <v>4</v>
+        <v>0.02</v>
       </c>
       <c r="E16">
-        <v>10</v>
+        <v>0.03</v>
       </c>
       <c r="F16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C17">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="E17">
-        <v>5</v>
+        <v>0.02</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C18">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D18">
         <v>0.01</v>
       </c>
       <c r="E18">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F18" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C19">
         <v>30</v>
       </c>
       <c r="D19">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="E19">
-        <v>0.04</v>
+        <v>0.15</v>
       </c>
       <c r="F19" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C20">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>0.12</v>
       </c>
       <c r="F20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -885,130 +888,130 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C21">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>0.06</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>0.18</v>
       </c>
       <c r="F21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C22">
         <v>100</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C23">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="D23">
-        <v>0.03</v>
+        <v>4</v>
       </c>
       <c r="E23">
-        <v>0.08</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C24">
         <v>40</v>
       </c>
       <c r="D24">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D25">
-        <v>0.01</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>0.03</v>
+        <v>6</v>
       </c>
       <c r="F25" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C26">
         <v>30</v>
       </c>
       <c r="D26">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E26">
-        <v>0.12</v>
+        <v>0.03</v>
       </c>
       <c r="F26" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
       </c>
       <c r="C27">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1017,178 +1020,178 @@
         <v>4</v>
       </c>
       <c r="F27" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C28">
-        <v>140</v>
+        <v>40</v>
       </c>
       <c r="D28">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="E28">
-        <v>0.06</v>
+        <v>5</v>
       </c>
       <c r="F28" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C29">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="D29">
         <v>1</v>
       </c>
       <c r="E29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F29" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
       </c>
       <c r="C30">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F30" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C31">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D31">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E31">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="F31" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B32" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C32">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="E32">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="F32" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C33">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="D33">
-        <v>0.01</v>
+        <v>40</v>
       </c>
       <c r="E33">
-        <v>0.03</v>
+        <v>120</v>
       </c>
       <c r="F33" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B34" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C34">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="D34">
-        <v>0.01</v>
+        <v>20</v>
       </c>
       <c r="E34">
-        <v>0.04</v>
+        <v>60</v>
       </c>
       <c r="F34" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C35">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="D35">
-        <v>0.06</v>
+        <v>20</v>
       </c>
       <c r="E35">
-        <v>0.18</v>
+        <v>60</v>
       </c>
       <c r="F35" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B36" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C36">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D36">
         <v>0.01</v>
@@ -1197,70 +1200,71 @@
         <v>0.03</v>
       </c>
       <c r="F36" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B37" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C37">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D37">
-        <v>20</v>
+        <v>0.01</v>
       </c>
       <c r="E37">
-        <v>60</v>
+        <v>0.04</v>
       </c>
       <c r="F37" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C38">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>0.01</v>
       </c>
       <c r="E38">
-        <v>6</v>
+        <v>0.04</v>
       </c>
       <c r="F38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B39" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C39">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="E39">
-        <v>4</v>
+        <v>0.06</v>
       </c>
       <c r="F39" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F39" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/EquipRandomPool.xlsx
+++ b/Data/EquipRandomPool.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{720F983E-8428-4184-B5D1-B0412433BD09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{245D3C63-6D24-471B-BC34-A4BC4EF090D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47130" yWindow="3180" windowWidth="21645" windowHeight="16245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipRandomPool" sheetId="3" r:id="rId1"/>
@@ -67,9 +67,6 @@
     <t>Evasion</t>
   </si>
   <si>
-    <t>Sword</t>
-  </si>
-  <si>
     <t>Helmet</t>
   </si>
   <si>
@@ -101,6 +98,9 @@
   </si>
   <si>
     <t>CritDmg_Inc</t>
+  </si>
+  <si>
+    <t>Bow</t>
   </si>
 </sst>
 </file>
@@ -505,19 +505,19 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>0.15</v>
       </c>
       <c r="F2" t="s">
         <v>20</v>
@@ -525,19 +525,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>0.03</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
@@ -545,19 +545,19 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C4">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>0.06</v>
       </c>
       <c r="F4" t="s">
         <v>20</v>
@@ -565,19 +565,19 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C5">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>0.03</v>
       </c>
       <c r="F5" t="s">
         <v>20</v>
@@ -585,33 +585,33 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C6">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
       <c r="C7">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -620,24 +620,24 @@
         <v>4</v>
       </c>
       <c r="F7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="C8">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>0.02</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>0.06</v>
       </c>
       <c r="F8" t="s">
         <v>20</v>
@@ -648,39 +648,39 @@
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E9">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="F9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C10">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D10">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>0.03</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -688,30 +688,30 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D11">
-        <v>0.01</v>
+        <v>2</v>
       </c>
       <c r="E11">
-        <v>0.03</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C12">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D12">
         <v>0.01</v>
@@ -720,67 +720,67 @@
         <v>0.03</v>
       </c>
       <c r="F12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C13">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="D13">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="E13">
-        <v>0.06</v>
+        <v>4</v>
       </c>
       <c r="F13" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C14">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="D14">
+        <v>0.01</v>
+      </c>
+      <c r="E14">
         <v>0.03</v>
       </c>
-      <c r="E14">
-        <v>0.08</v>
-      </c>
       <c r="F14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C15">
+        <v>120</v>
+      </c>
+      <c r="D15">
         <v>30</v>
       </c>
-      <c r="D15">
-        <v>0.01</v>
-      </c>
       <c r="E15">
-        <v>0.03</v>
+        <v>90</v>
       </c>
       <c r="F15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -788,50 +788,50 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C16">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="D16">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="E16">
-        <v>0.03</v>
+        <v>4</v>
       </c>
       <c r="F16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C17">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="D17">
-        <v>0.01</v>
+        <v>3</v>
       </c>
       <c r="E17">
-        <v>0.02</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
         <v>11</v>
       </c>
       <c r="C18">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D18">
         <v>0.01</v>
@@ -840,7 +840,7 @@
         <v>0.02</v>
       </c>
       <c r="F18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -848,76 +848,76 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19">
         <v>25</v>
       </c>
-      <c r="C19">
-        <v>30</v>
-      </c>
       <c r="D19">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="E19">
-        <v>0.15</v>
+        <v>4</v>
       </c>
       <c r="F19" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C20">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D20">
-        <v>0.05</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>0.12</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C21">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="D21">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="E21">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="F21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C22">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>0.01</v>
       </c>
       <c r="E22">
-        <v>8</v>
+        <v>0.02</v>
       </c>
       <c r="F22" t="s">
         <v>20</v>
@@ -928,16 +928,16 @@
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C23">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>0.03</v>
       </c>
       <c r="E23">
-        <v>10</v>
+        <v>0.08</v>
       </c>
       <c r="F23" t="s">
         <v>20</v>
@@ -945,19 +945,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>0.01</v>
       </c>
       <c r="E24">
-        <v>6</v>
+        <v>0.03</v>
       </c>
       <c r="F24" t="s">
         <v>20</v>
@@ -965,13 +965,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C25">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -980,7 +980,7 @@
         <v>6</v>
       </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -988,36 +988,36 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C26">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D26">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="E26">
-        <v>0.03</v>
+        <v>4</v>
       </c>
       <c r="F26" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C27">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>0.04</v>
       </c>
       <c r="F27" t="s">
         <v>20</v>
@@ -1025,27 +1025,27 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C28">
         <v>40</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E28">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="F28" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -1057,10 +1057,10 @@
         <v>1</v>
       </c>
       <c r="E29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -1068,36 +1068,36 @@
         <v>18</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C30">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30">
         <v>6</v>
       </c>
       <c r="F30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C31">
-        <v>20</v>
+        <v>120</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>0.06</v>
       </c>
       <c r="E31">
-        <v>4</v>
+        <v>0.18</v>
       </c>
       <c r="F31" t="s">
         <v>20</v>
@@ -1105,19 +1105,19 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B32" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C32">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="D32">
-        <v>30</v>
+        <v>0.01</v>
       </c>
       <c r="E32">
-        <v>90</v>
+        <v>0.03</v>
       </c>
       <c r="F32" t="s">
         <v>20</v>
@@ -1125,19 +1125,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B33" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C33">
-        <v>140</v>
+        <v>30</v>
       </c>
       <c r="D33">
-        <v>40</v>
+        <v>0.01</v>
       </c>
       <c r="E33">
-        <v>120</v>
+        <v>0.04</v>
       </c>
       <c r="F33" t="s">
         <v>20</v>
@@ -1145,42 +1145,42 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B34" t="s">
         <v>7</v>
       </c>
       <c r="C34">
+        <v>140</v>
+      </c>
+      <c r="D34">
         <v>40</v>
       </c>
-      <c r="D34">
-        <v>20</v>
-      </c>
       <c r="E34">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F34" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B35" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C35">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D35">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E35">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="F35" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -1188,27 +1188,27 @@
         <v>15</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C36">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D36">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="E36">
-        <v>0.03</v>
+        <v>5</v>
       </c>
       <c r="F36" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C37">
         <v>30</v>
@@ -1217,54 +1217,58 @@
         <v>0.01</v>
       </c>
       <c r="E37">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F37" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38">
+        <v>140</v>
+      </c>
+      <c r="D38">
+        <v>4</v>
+      </c>
+      <c r="E38">
         <v>10</v>
       </c>
-      <c r="C38">
-        <v>120</v>
-      </c>
-      <c r="D38">
-        <v>0.01</v>
-      </c>
-      <c r="E38">
-        <v>0.04</v>
-      </c>
       <c r="F38" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B39" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C39">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="D39">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>0.06</v>
+        <v>4</v>
       </c>
       <c r="F39" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F39" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A1:F39" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F39">
+      <sortCondition descending="1" ref="A1:A39"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
